--- a/public/samples/bb-templates/BB-Template-Import-audax-vii.xlsx
+++ b/public/samples/bb-templates/BB-Template-Import-audax-vii.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,6 +444,9 @@
       <c r="M1" t="str">
         <v>detect_keys</v>
       </c>
+      <c r="N1" t="str">
+        <v>auto_discover_tabs</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -456,7 +459,7 @@
         <v>B</v>
       </c>
       <c r="D2" t="str">
-        <v>Investor List</v>
+        <v/>
       </c>
       <c r="E2">
         <v>13</v>
@@ -485,10 +488,13 @@
       <c r="M2" t="str">
         <v/>
       </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -528,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>Investor List</v>
+        <v/>
       </c>
       <c r="D2">
         <v>13</v>
@@ -752,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Borrowers listed at rows 9-10.</v>
+        <v>One visible tab per deal/borrower sleeve; extraction auto-discovers tabs and maps each sheet name into Fund Sleeve.</v>
       </c>
     </row>
     <row r="3">
@@ -760,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Source detail reads "Column 13: Column Headers" — verify whether headers sit at row 13 or the table begins at spreadsheet column 13.</v>
+        <v>Borrowers listed at rows 9-10. Column headers are on Excel row 13.</v>
       </c>
     </row>
   </sheetData>
